--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2023_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:49</t>
+    <t xml:space="preserve">2026-09-24 01:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -806,7 +806,7 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>345</v>
@@ -820,7 +820,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>345</v>
@@ -834,7 +834,7 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.07</v>
+        <v>0.13</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>345</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2023_arica_y_parinacota.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:38</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2023_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 20:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
